--- a/inventory/matter-inventory.template.xlsx
+++ b/inventory/matter-inventory.template.xlsx
@@ -62,7 +62,7 @@
     <t>MVA Personal Injury</t>
   </si>
   <si>
-    <t>Open</t>
+    <t>Litigation</t>
   </si>
   <si>
     <t>brennan@collinsattorneys.com</t>
@@ -157,7 +157,7 @@
     <col min="3" max="3" width="14.6739501953125" customWidth="1"/>
     <col min="4" max="4" width="18.74881935119629" customWidth="1"/>
     <col min="5" max="5" width="19.349079132080078" customWidth="1"/>
-    <col min="6" max="6" width="9.262957572937012" customWidth="1"/>
+    <col min="6" max="6" width="9.572667121887207" customWidth="1"/>
     <col min="7" max="7" width="28.966917037963867" customWidth="1"/>
     <col min="8" max="8" width="50.67942428588867" customWidth="1"/>
     <col min="9" max="9" width="24.66827392578125" customWidth="1"/>
@@ -237,8 +237,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="F2:F1000" showErrorMessage="1" errorTitle="Invalid Status" error="Status must be Prospective, Open, Closed, or Intake.">
-      <formula1>"Prospective,Open,Closed,Intake"</formula1>
+    <dataValidation type="list" sqref="F2:F1000" showErrorMessage="1" errorTitle="Invalid Status" error="Status must be Eval, Pre-Litigation, Litigation, or Closed.">
+      <formula1>"Eval,Pre-Litigation,Litigation,Closed"</formula1>
     </dataValidation>
   </dataValidations>
   <headerFooter/>
